--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.04444888775235</v>
+        <v>4.394722944259757</v>
       </c>
       <c r="D2" t="n">
-        <v>26.40376887973456</v>
+        <v>4.290612442956867</v>
       </c>
       <c r="E2" t="n">
-        <v>14.10960248240802</v>
+        <v>2.292810403391303</v>
       </c>
       <c r="F2" t="n">
-        <v>11.40565918007053</v>
+        <v>1.853419616761462</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.4627509408249</v>
+        <v>6.575197027884047</v>
       </c>
       <c r="D3" t="n">
-        <v>32.99904063816791</v>
+        <v>5.362344103702286</v>
       </c>
       <c r="E3" t="n">
-        <v>14.10960248240802</v>
+        <v>2.292810403391303</v>
       </c>
       <c r="F3" t="n">
-        <v>11.40565918007053</v>
+        <v>1.853419616761462</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.170528158926303</v>
+        <v>1.002710825825524</v>
       </c>
       <c r="D4" t="n">
-        <v>6.190182570005358</v>
+        <v>1.005904667625871</v>
       </c>
       <c r="E4" t="n">
-        <v>14.10960248240802</v>
+        <v>2.292810403391303</v>
       </c>
       <c r="F4" t="n">
-        <v>11.40565918007053</v>
+        <v>1.853419616761462</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
